--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.11553759848937</v>
+        <v>0.6687748597545227</v>
       </c>
       <c r="D2" t="n">
-        <v>3.952768736506205</v>
+        <v>0.6423249196822582</v>
       </c>
       <c r="E2" t="n">
-        <v>14.07764373971708</v>
+        <v>2.287617107704026</v>
       </c>
       <c r="F2" t="n">
-        <v>14.06187957203295</v>
+        <v>2.285055430455355</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.90547533988396</v>
+        <v>8.109639742731144</v>
       </c>
       <c r="D3" t="n">
-        <v>49.71716042784718</v>
+        <v>8.079038569525167</v>
       </c>
       <c r="E3" t="n">
-        <v>14.07764373971708</v>
+        <v>2.287617107704026</v>
       </c>
       <c r="F3" t="n">
-        <v>14.06187957203295</v>
+        <v>2.285055430455355</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.75627887385064</v>
+        <v>4.672895317000728</v>
       </c>
       <c r="D4" t="n">
-        <v>28.53292054029432</v>
+        <v>4.636599587797827</v>
       </c>
       <c r="E4" t="n">
-        <v>14.07764373971708</v>
+        <v>2.287617107704026</v>
       </c>
       <c r="F4" t="n">
-        <v>14.06187957203295</v>
+        <v>2.285055430455355</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.14497397404092</v>
+        <v>8.798558270781649</v>
       </c>
       <c r="D5" t="n">
-        <v>54.02547382684856</v>
+        <v>8.779139496862891</v>
       </c>
       <c r="E5" t="n">
-        <v>14.07764373971708</v>
+        <v>2.287617107704026</v>
       </c>
       <c r="F5" t="n">
-        <v>14.06187957203295</v>
+        <v>2.285055430455355</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.69766004686736</v>
+        <v>5.638369757615947</v>
       </c>
       <c r="D6" t="n">
-        <v>34.56768593034474</v>
+        <v>5.61724896368102</v>
       </c>
       <c r="E6" t="n">
-        <v>14.07764373971708</v>
+        <v>2.287617107704026</v>
       </c>
       <c r="F6" t="n">
-        <v>14.06187957203295</v>
+        <v>2.285055430455355</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.55628761731398</v>
+        <v>4.802896737813521</v>
       </c>
       <c r="D7" t="n">
-        <v>29.46164218184343</v>
+        <v>4.787516854549557</v>
       </c>
       <c r="E7" t="n">
-        <v>14.07764373971708</v>
+        <v>2.287617107704026</v>
       </c>
       <c r="F7" t="n">
-        <v>14.06187957203295</v>
+        <v>2.285055430455355</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.41300294762183</v>
+        <v>5.917112978988547</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46194709138324</v>
+        <v>5.925066402349778</v>
       </c>
       <c r="E8" t="n">
-        <v>14.07764373971708</v>
+        <v>2.287617107704026</v>
       </c>
       <c r="F8" t="n">
-        <v>14.06187957203295</v>
+        <v>2.285055430455355</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.6153461231036</v>
+        <v>4.974993745004335</v>
       </c>
       <c r="D9" t="n">
-        <v>30.62689237832508</v>
+        <v>4.976870011477826</v>
       </c>
       <c r="E9" t="n">
-        <v>14.07764373971708</v>
+        <v>2.287617107704026</v>
       </c>
       <c r="F9" t="n">
-        <v>14.06187957203295</v>
+        <v>2.285055430455355</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>49.69998775233367</v>
+        <v>8.076248009754222</v>
       </c>
       <c r="D10" t="n">
-        <v>49.66548828737299</v>
+        <v>8.070641846698113</v>
       </c>
       <c r="E10" t="n">
-        <v>14.07764373971708</v>
+        <v>2.287617107704026</v>
       </c>
       <c r="F10" t="n">
-        <v>14.06187957203295</v>
+        <v>2.285055430455355</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.01349034619116</v>
+        <v>3.902192181256064</v>
       </c>
       <c r="D11" t="n">
-        <v>24.07644900970548</v>
+        <v>3.912422964077141</v>
       </c>
       <c r="E11" t="n">
-        <v>14.07764373971708</v>
+        <v>2.287617107704026</v>
       </c>
       <c r="F11" t="n">
-        <v>14.06187957203295</v>
+        <v>2.285055430455355</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>16.40664066980995</v>
+        <v>2.666079108844118</v>
       </c>
       <c r="D12" t="n">
-        <v>16.60372259049946</v>
+        <v>2.698104920956163</v>
       </c>
       <c r="E12" t="n">
-        <v>14.07764373971708</v>
+        <v>2.287617107704026</v>
       </c>
       <c r="F12" t="n">
-        <v>14.06187957203295</v>
+        <v>2.285055430455355</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>44.38522259571699</v>
+        <v>7.212598671804011</v>
       </c>
       <c r="D13" t="n">
-        <v>44.4886945778273</v>
+        <v>7.229412868896936</v>
       </c>
       <c r="E13" t="n">
-        <v>14.07764373971708</v>
+        <v>2.287617107704026</v>
       </c>
       <c r="F13" t="n">
-        <v>14.06187957203295</v>
+        <v>2.285055430455355</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
